--- a/GameDesign/Excel/Mail.xlsx
+++ b/GameDesign/Excel/Mail.xlsx
@@ -467,13 +467,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="47" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="54" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
@@ -482,7 +482,7 @@
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="41" customWidth="1" min="13" max="13"/>
+    <col width="46" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -966,6 +966,201 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>경매 구매</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>경매장에서 구매한 물품입니다.</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>경매장</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1" t="n"/>
+      <c r="J12" s="1" t="n"/>
+      <c r="K12" s="1" t="n"/>
+      <c r="L12" s="1" t="n"/>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>경매 즉시구매 — 첨부는 서버가 채운다(T-087)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>경매 판매 대금</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>물품이 판매되었습니다. 판매 수수료를 뺀 대금입니다.</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>경매장</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1" t="n"/>
+      <c r="J13" s="1" t="n"/>
+      <c r="K13" s="1" t="n"/>
+      <c r="L13" s="1" t="n"/>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>경매 판매 대금 — 첨부는 서버가 채운다(T-087)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>경매 취소 반환</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>판매를 취소한 물품을 돌려드립니다.</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>경매장</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1" t="n"/>
+      <c r="J14" s="1" t="n"/>
+      <c r="K14" s="1" t="n"/>
+      <c r="L14" s="1" t="n"/>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>취소 반환 — 등록비는 돌려주지 않는다(T-087)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>경매 만료 반환</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>기간 안에 팔리지 않은 물품과 등록비를 돌려드립니다.</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>경매장</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1" t="n"/>
+      <c r="J15" s="1" t="n"/>
+      <c r="K15" s="1" t="n"/>
+      <c r="L15" s="1" t="n"/>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>만료 반환 — 등록비 환급(T-087)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n"/>
+      <c r="B16" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>경매 등록 실패 반환</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>경매장에 등록하지 못한 물품과 등록비를 돌려드립니다.</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>경매장</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1" t="n"/>
+      <c r="J16" s="1" t="n"/>
+      <c r="K16" s="1" t="n"/>
+      <c r="L16" s="1" t="n"/>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>등록 거부·유실 반환 — 등록비 환급(T-087)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/GameDesign/Excel/Mail.xlsx
+++ b/GameDesign/Excel/Mail.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -477,11 +477,11 @@
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
     <col width="46" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
@@ -498,7 +498,6 @@
       <c r="J1" s="1" t="n"/>
       <c r="K1" s="1" t="n"/>
       <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -538,30 +537,25 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>다이아</t>
+          <t>아이템</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>아이템 수량</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>아이템 수량</t>
+          <t>캐릭터</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>캐릭터</t>
+          <t>장비</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>장비</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -628,11 +622,6 @@
           <t>a</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -672,7 +661,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>int[]</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -691,11 +680,6 @@
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>int[]</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -719,14 +703,11 @@
       <c r="G5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="H5" s="4" t="n"/>
       <c r="I5" s="4" t="n"/>
       <c r="J5" s="4" t="n"/>
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
-      <c r="M5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -745,7 +726,6 @@
       <c r="J6" s="4" t="n"/>
       <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
-      <c r="M6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -759,7 +739,11 @@
       <c r="E7" s="4" t="n"/>
       <c r="F7" s="4" t="n"/>
       <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
           <t>""</t>
@@ -776,11 +760,6 @@
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>""</t>
         </is>
@@ -798,24 +777,23 @@
       <c r="E8" s="4" t="n"/>
       <c r="F8" s="4" t="n"/>
       <c r="G8" s="4" t="n"/>
-      <c r="H8" s="4" t="n"/>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>ItemTable.ItemTID?</t>
         </is>
       </c>
-      <c r="J8" s="4" t="n"/>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>CharacterTable.CharacterTID?</t>
+        </is>
+      </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>CharacterTable.CharacterTID?</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
           <t>EquipTable.EquipTID?</t>
         </is>
       </c>
-      <c r="M8" s="4" t="n"/>
+      <c r="L8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -851,30 +829,25 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>Dia</t>
+          <t>ItemTIDs</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>ItemTIDs</t>
+          <t>ItemCounts</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>ItemCounts</t>
+          <t>CharacterTIDs</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>CharacterTIDs</t>
+          <t>EquipTIDs</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>EquipTIDs</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -906,22 +879,19 @@
       <c r="G10" s="6" t="n">
         <v>1000</v>
       </c>
-      <c r="H10" s="6" t="n">
-        <v>0</v>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>100007</t>
+        </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>100007</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
           <t>3</t>
         </is>
       </c>
+      <c r="J10" s="1" t="n"/>
       <c r="K10" s="1" t="n"/>
-      <c r="L10" s="1" t="n"/>
-      <c r="M10" s="7" t="inlineStr">
+      <c r="L10" s="7" t="inlineStr">
         <is>
           <t>테스트 — 운영 우편</t>
         </is>
@@ -953,14 +923,11 @@
       <c r="G11" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="H11" s="1" t="n"/>
       <c r="I11" s="1" t="n"/>
       <c r="J11" s="1" t="n"/>
       <c r="K11" s="1" t="n"/>
-      <c r="L11" s="1" t="n"/>
-      <c r="M11" s="7" t="inlineStr">
+      <c r="L11" s="7" t="inlineStr">
         <is>
           <t>넘침 보관 — 첨부는 서버가 채운다(T-082)</t>
         </is>
@@ -992,14 +959,11 @@
       <c r="G12" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="H12" s="1" t="n"/>
       <c r="I12" s="1" t="n"/>
       <c r="J12" s="1" t="n"/>
       <c r="K12" s="1" t="n"/>
-      <c r="L12" s="1" t="n"/>
-      <c r="M12" s="7" t="inlineStr">
+      <c r="L12" s="7" t="inlineStr">
         <is>
           <t>경매 즉시구매 — 첨부는 서버가 채운다(T-087)</t>
         </is>
@@ -1031,14 +995,11 @@
       <c r="G13" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="H13" s="1" t="n"/>
       <c r="I13" s="1" t="n"/>
       <c r="J13" s="1" t="n"/>
       <c r="K13" s="1" t="n"/>
-      <c r="L13" s="1" t="n"/>
-      <c r="M13" s="7" t="inlineStr">
+      <c r="L13" s="7" t="inlineStr">
         <is>
           <t>경매 판매 대금 — 첨부는 서버가 채운다(T-087)</t>
         </is>
@@ -1070,14 +1031,11 @@
       <c r="G14" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="H14" s="1" t="n"/>
       <c r="I14" s="1" t="n"/>
       <c r="J14" s="1" t="n"/>
       <c r="K14" s="1" t="n"/>
-      <c r="L14" s="1" t="n"/>
-      <c r="M14" s="7" t="inlineStr">
+      <c r="L14" s="7" t="inlineStr">
         <is>
           <t>취소 반환 — 등록비는 돌려주지 않는다(T-087)</t>
         </is>
@@ -1109,14 +1067,11 @@
       <c r="G15" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="H15" s="1" t="n"/>
       <c r="I15" s="1" t="n"/>
       <c r="J15" s="1" t="n"/>
       <c r="K15" s="1" t="n"/>
-      <c r="L15" s="1" t="n"/>
-      <c r="M15" s="7" t="inlineStr">
+      <c r="L15" s="7" t="inlineStr">
         <is>
           <t>만료 반환 — 등록비 환급(T-087)</t>
         </is>
@@ -1148,14 +1103,11 @@
       <c r="G16" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="H16" s="1" t="n"/>
       <c r="I16" s="1" t="n"/>
       <c r="J16" s="1" t="n"/>
       <c r="K16" s="1" t="n"/>
-      <c r="L16" s="1" t="n"/>
-      <c r="M16" s="7" t="inlineStr">
+      <c r="L16" s="7" t="inlineStr">
         <is>
           <t>등록 거부·유실 반환 — 등록비 환급(T-087)</t>
         </is>

--- a/GameDesign/Excel/Mail.xlsx
+++ b/GameDesign/Excel/Mail.xlsx
@@ -881,7 +881,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>100007</t>
+          <t>100019</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">

--- a/GameDesign/Excel/Mail.xlsx
+++ b/GameDesign/Excel/Mail.xlsx
@@ -474,7 +474,7 @@
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="54" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -636,17 +636,17 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>lstring</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>lstring</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>lstring</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
